--- a/assessment_forms/012_delivery_impact_assessment_form--assessment_forms.xlsx
+++ b/assessment_forms/012_delivery_impact_assessment_form--assessment_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,13 +437,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
     <col width="22" customWidth="1" min="2" max="2"/>
     <col width="41" customWidth="1" min="3" max="3"/>
-    <col width="29" customWidth="1" min="4" max="4"/>
+    <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
@@ -686,14 +686,10 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Contact Details</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
           <t>Provide contact information</t>
         </is>
       </c>
+      <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
           <t>no</t>
@@ -726,17 +722,17 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>delivery_frequency_2</t>
+          <t>contact_person</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>How often do deliveries occur?</t>
+          <t>Contact Person</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -749,17 +745,17 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>delivery_time_2</t>
+          <t>service_quality_2</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Delivery Time</t>
+          <t>How would you rate the service quality?</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -772,17 +768,17 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>contact_person</t>
+          <t>delivery_frequency_2</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Contact Person</t>
+          <t>Delivery Frequency 2</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -795,297 +791,21 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>service_quality_2</t>
+          <t>delivery_time_2</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>How would you rate the service quality?</t>
+          <t>Delivery Time 2</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>delivery_frequency_3</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>How often do deliveries occur?</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>delivery_location_2</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Where do deliveries occur?</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>contact_details_2</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Provide additional contact information</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>delivery_frequency_4</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>How often do deliveries occur?</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>service_type_2</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Service Type</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>time</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>delivery_time_3</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Delivery Time</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>contact_person_2</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Contact Person</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>service_type_3</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Service Type</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>service_quality_3</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>How would you rate the service quality?</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>service_quality_4</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>How would you rate the service quality?</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>delivery_frequency_5</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>How often do deliveries occur?</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>delivery_location_3</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Where do deliveries occur?</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -1102,7 +822,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C42"/>
+  <dimension ref="A1:C20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -1135,12 +855,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1152,12 +872,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1169,12 +889,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1186,12 +906,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1254,12 +974,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1271,12 +991,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1334,68 +1054,68 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>delivery_frequency_2_choices</t>
+          <t>contact_person_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>delivery_frequency_2_choices</t>
+          <t>contact_person_choices</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>contact_person_choices</t>
+          <t>service_quality_2_choices</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>excellent</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Excellent</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>contact_person_choices</t>
+          <t>service_quality_2_choices</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>good</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Good</t>
         </is>
       </c>
     </row>
@@ -1407,420 +1127,46 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>excellent</t>
+          <t>fair</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Excellent</t>
+          <t>Fair</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>service_quality_2_choices</t>
+          <t>delivery_frequency_2_choices</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>good</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Good</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>service_quality_2_choices</t>
+          <t>delivery_frequency_2_choices</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>fair</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Fair</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>delivery_frequency_3_choices</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>delivery_frequency_3_choices</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>delivery_location_2_choices</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>delivery_location_2_choices</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>delivery_frequency_4_choices</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>delivery_frequency_4_choices</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>service_type_2_choices</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>service_type_2_choices</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>contact_person_2_choices</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>contact_person_2_choices</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>service_type_3_choices</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>service_type_3_choices</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>service_quality_3_choices</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>excellent</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Excellent</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>service_quality_3_choices</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>good</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Good</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>service_quality_3_choices</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>fair</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Fair</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>service_quality_4_choices</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>excellent</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Excellent</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>service_quality_4_choices</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>good</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Good</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>service_quality_4_choices</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>fair</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Fair</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>delivery_frequency_5_choices</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>delivery_frequency_5_choices</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>delivery_location_3_choices</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>delivery_location_3_choices</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>No</t>
+          <t>False</t>
         </is>
       </c>
     </row>
